--- a/StructureDefinition-tk-api-specification-category.xlsx
+++ b/StructureDefinition-tk-api-specification-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T07:38:29+00:00</t>
+    <t>2026-10-19T12:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-api-specification-category.xlsx
+++ b/StructureDefinition-tk-api-specification-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:45:34+00:00</t>
+    <t>2026-10-19T13:06:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-api-specification-category.xlsx
+++ b/StructureDefinition-tk-api-specification-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:06:20+00:00</t>
+    <t>2026-10-26T20:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-api-specification-category.xlsx
+++ b/StructureDefinition-tk-api-specification-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:15:49+00:00</t>
+    <t>2026-10-26T20:25:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-api-specification-category.xlsx
+++ b/StructureDefinition-tk-api-specification-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:25:02+00:00</t>
+    <t>2026-10-27T17:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-tk-api-specification-category.xlsx
+++ b/StructureDefinition-tk-api-specification-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T17:54:53+00:00</t>
+    <t>2026-10-28T11:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
